--- a/data/trans_dic/P2A_fisi_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2A_fisi_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad física</t>
+          <t>Hogares con personas con limitación por discapacidad física (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,27</t>
+          <t>1,72; 4,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,07; 7,72</t>
+          <t>3,97; 7,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,17; 9,09</t>
+          <t>5,15; 9,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,43; 15,41</t>
+          <t>10,44; 15,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,55; 6,77</t>
+          <t>3,47; 6,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,06; 10,37</t>
+          <t>6,06; 10,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,28; 9,2</t>
+          <t>5,28; 9,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,04; 12,4</t>
+          <t>8,38; 12,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,97; 5,06</t>
+          <t>2,92; 5,04</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,67; 8,32</t>
+          <t>5,64; 8,35</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,73; 8,7</t>
+          <t>5,73; 8,54</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,86; 13,39</t>
+          <t>9,91; 13,21</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,14; 7,18</t>
+          <t>4,06; 7,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,51; 10,08</t>
+          <t>6,44; 10,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,85; 6,59</t>
+          <t>3,78; 6,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,44; 13,06</t>
+          <t>4,38; 13,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,37; 7,44</t>
+          <t>4,43; 7,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,15; 12,05</t>
+          <t>8,3; 12,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,5; 9,09</t>
+          <t>5,71; 9,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,74; 15,23</t>
+          <t>11,71; 15,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,51; 6,8</t>
+          <t>4,58; 6,64</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,71; 10,46</t>
+          <t>7,77; 10,31</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,07; 7,26</t>
+          <t>5,08; 7,37</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,45; 13,33</t>
+          <t>7,49; 13,32</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,3; 7,74</t>
+          <t>4,19; 8,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,62; 9,56</t>
+          <t>5,63; 9,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,66</t>
+          <t>2,03; 4,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,0; 15,75</t>
+          <t>10,04; 15,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,27; 7,9</t>
+          <t>4,37; 7,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,35; 10,75</t>
+          <t>6,14; 10,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,62; 6,88</t>
+          <t>3,63; 6,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,5; 60,64</t>
+          <t>10,53; 64,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,68; 7,24</t>
+          <t>4,64; 7,15</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,53; 9,53</t>
+          <t>6,51; 9,44</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,19; 5,47</t>
+          <t>3,22; 5,51</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,32; 47,88</t>
+          <t>11,39; 47,42</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,23; 7,24</t>
+          <t>4,14; 7,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,86; 9,64</t>
+          <t>5,67; 9,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,54; 8,95</t>
+          <t>5,48; 8,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,58; 9,99</t>
+          <t>6,62; 9,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,17; 9,47</t>
+          <t>6,08; 9,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,02; 11,61</t>
+          <t>7,87; 11,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,36; 9,89</t>
+          <t>6,22; 9,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,71; 10,17</t>
+          <t>6,69; 10,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,64; 7,93</t>
+          <t>5,69; 7,9</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,36; 10,04</t>
+          <t>7,47; 10,07</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,33; 8,71</t>
+          <t>6,29; 8,88</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,0; 9,61</t>
+          <t>6,99; 9,58</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,26; 5,83</t>
+          <t>4,3; 5,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,39; 8,27</t>
+          <t>6,48; 8,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,74; 6,36</t>
+          <t>4,78; 6,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,35; 11,76</t>
+          <t>8,11; 11,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,42; 7,13</t>
+          <t>5,49; 7,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,09; 10,04</t>
+          <t>8,12; 10,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,05; 7,77</t>
+          <t>6,07; 7,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,52; 31,24</t>
+          <t>10,51; 31,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,08; 6,25</t>
+          <t>5,13; 6,22</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,55; 8,89</t>
+          <t>7,56; 8,9</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,65; 6,89</t>
+          <t>5,61; 6,87</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,32; 22,62</t>
+          <t>10,27; 21,01</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad física</t>
+          <t>Hogares con personas con limitación por discapacidad física (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11257; 29606</t>
+          <t>11907; 29581</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28610; 54324</t>
+          <t>27956; 54350</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34870; 61329</t>
+          <t>34777; 62218</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>66268; 97901</t>
+          <t>66328; 98786</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>24406; 46579</t>
+          <t>23903; 46399</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>42224; 72290</t>
+          <t>42211; 70909</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35520; 61928</t>
+          <t>35494; 63748</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>58289; 89947</t>
+          <t>60807; 90440</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>41099; 70010</t>
+          <t>40311; 69656</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>79353; 116551</t>
+          <t>79011; 116995</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>77261; 117224</t>
+          <t>77178; 115113</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>134105; 182146</t>
+          <t>134900; 179694</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39780; 69058</t>
+          <t>39027; 68437</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>66258; 102656</t>
+          <t>65570; 102786</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39355; 67351</t>
+          <t>38607; 68429</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>64900; 155773</t>
+          <t>52198; 156152</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>42354; 72031</t>
+          <t>42852; 74136</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>84083; 124393</t>
+          <t>85666; 124037</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57373; 94844</t>
+          <t>59533; 95627</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>112506; 146019</t>
+          <t>112291; 145544</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>86986; 131247</t>
+          <t>88444; 128260</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>157999; 214385</t>
+          <t>159271; 211393</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>104800; 149927</t>
+          <t>104847; 152251</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>160225; 286820</t>
+          <t>161070; 286541</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>29168; 52490</t>
+          <t>28456; 54369</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>42579; 72432</t>
+          <t>42630; 73640</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15470; 35378</t>
+          <t>15402; 35979</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>70456; 111004</t>
+          <t>70780; 108565</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>29211; 54042</t>
+          <t>29904; 54650</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>49342; 83511</t>
+          <t>47694; 83723</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28382; 54010</t>
+          <t>28496; 54700</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>98029; 566033</t>
+          <t>98240; 603392</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>63762; 98651</t>
+          <t>63162; 97419</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>100171; 146225</t>
+          <t>99884; 144960</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>49334; 84425</t>
+          <t>49783; 85084</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>185443; 784251</t>
+          <t>186535; 776728</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39893; 68213</t>
+          <t>38974; 67107</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>55519; 91358</t>
+          <t>53694; 91432</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>51963; 83929</t>
+          <t>51412; 81439</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>60947; 92586</t>
+          <t>61379; 92070</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>64041; 98345</t>
+          <t>63138; 98671</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>84324; 122175</t>
+          <t>82809; 122937</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>66422; 103214</t>
+          <t>64970; 102571</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>73429; 111401</t>
+          <t>73245; 111675</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>111805; 157008</t>
+          <t>112754; 156576</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>147153; 200694</t>
+          <t>149444; 201345</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>125337; 172638</t>
+          <t>124625; 176006</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>141439; 194242</t>
+          <t>141251; 193633</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>139518; 191126</t>
+          <t>140911; 188514</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>219117; 283385</t>
+          <t>222019; 282813</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>161060; 215899</t>
+          <t>162097; 216780</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>288845; 406715</t>
+          <t>280643; 412039</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>183046; 240842</t>
+          <t>185394; 242778</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>287725; 357100</t>
+          <t>289062; 360613</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>214419; 275554</t>
+          <t>215180; 277386</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>390677; 1159719</t>
+          <t>390238; 1157341</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>338131; 415727</t>
+          <t>341330; 414212</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>527507; 620899</t>
+          <t>527858; 621491</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>392163; 478357</t>
+          <t>389233; 476535</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>739944; 1622589</t>
+          <t>736831; 1507037</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_fisi_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2A_fisi_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,26</t>
+          <t>1,74; 4,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,97; 7,73</t>
+          <t>3,99; 7,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,15; 9,22</t>
+          <t>5,21; 9,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,44; 15,55</t>
+          <t>10,07; 15,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,47; 6,74</t>
+          <t>3,66; 6,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,06; 10,17</t>
+          <t>6,11; 10,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,28; 9,47</t>
+          <t>5,12; 9,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,38; 12,47</t>
+          <t>9,48; 13,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,92; 5,04</t>
+          <t>2,97; 4,89</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,64; 8,35</t>
+          <t>5,54; 8,23</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,73; 8,54</t>
+          <t>5,74; 8,45</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,91; 13,21</t>
+          <t>10,33; 13,33</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,06; 7,12</t>
+          <t>4,12; 7,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,44; 10,1</t>
+          <t>6,51; 10,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,78; 6,69</t>
+          <t>3,7; 6,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,38; 13,09</t>
+          <t>9,79; 14,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,43; 7,66</t>
+          <t>4,34; 7,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,3; 12,02</t>
+          <t>8,24; 12,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,71; 9,17</t>
+          <t>5,65; 9,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,71; 15,18</t>
+          <t>11,72; 15,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,58; 6,64</t>
+          <t>4,52; 6,76</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,77; 10,31</t>
+          <t>7,78; 10,5</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,08; 7,37</t>
+          <t>5,12; 7,35</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,49; 13,32</t>
+          <t>11,35; 14,11</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,19; 8,01</t>
+          <t>4,19; 7,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,63; 9,72</t>
+          <t>5,64; 9,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 4,74</t>
+          <t>2,08; 4,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,04; 15,41</t>
+          <t>9,66; 14,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,37; 7,99</t>
+          <t>4,23; 8,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,14; 10,77</t>
+          <t>6,51; 10,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,63; 6,97</t>
+          <t>3,63; 7,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,53; 64,65</t>
+          <t>10,28; 14,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,64; 7,15</t>
+          <t>4,63; 7,26</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,51; 9,44</t>
+          <t>6,5; 9,28</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,22; 5,51</t>
+          <t>3,17; 5,38</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,39; 47,42</t>
+          <t>10,71; 13,7</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,14; 7,12</t>
+          <t>4,12; 7,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,67; 9,65</t>
+          <t>5,95; 9,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,48; 8,69</t>
+          <t>5,48; 8,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,62; 9,93</t>
+          <t>6,44; 9,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,08; 9,5</t>
+          <t>6,32; 9,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,87; 11,69</t>
+          <t>7,79; 11,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,22; 9,83</t>
+          <t>6,28; 9,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,69; 10,2</t>
+          <t>7,87; 10,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,69; 7,9</t>
+          <t>5,59; 7,81</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,47; 10,07</t>
+          <t>7,3; 10,01</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,29; 8,88</t>
+          <t>6,37; 8,75</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,99; 9,58</t>
+          <t>7,64; 9,81</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,3; 5,75</t>
+          <t>4,23; 5,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,48; 8,25</t>
+          <t>6,37; 8,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,78; 6,39</t>
+          <t>4,83; 6,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,11; 11,91</t>
+          <t>9,81; 11,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,49; 7,18</t>
+          <t>5,4; 7,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,12; 10,13</t>
+          <t>8,08; 10,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,07; 7,83</t>
+          <t>6,01; 7,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,51; 31,18</t>
+          <t>10,65; 12,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,13; 6,22</t>
+          <t>5,08; 6,19</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,56; 8,9</t>
+          <t>7,56; 8,98</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,61; 6,87</t>
+          <t>5,65; 6,78</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,27; 21,01</t>
+          <t>10,52; 11,87</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81254</t>
+          <t>85517</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>75702</t>
+          <t>81007</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>156956</t>
+          <t>166524</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11907; 29581</t>
+          <t>12065; 29315</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>27956; 54350</t>
+          <t>28066; 54691</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34777; 62218</t>
+          <t>35159; 61365</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>66328; 98786</t>
+          <t>69536; 104370</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23903; 46399</t>
+          <t>25213; 45708</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>42211; 70909</t>
+          <t>42561; 71776</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35494; 63748</t>
+          <t>34473; 61833</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>60807; 90440</t>
+          <t>69596; 97235</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>40311; 69656</t>
+          <t>41032; 67545</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>79011; 116995</t>
+          <t>77573; 115292</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>77178; 115113</t>
+          <t>77297; 113911</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>134900; 179694</t>
+          <t>147182; 189953</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>116030</t>
+          <t>124258</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>128812</t>
+          <t>143077</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>244842</t>
+          <t>267335</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39027; 68437</t>
+          <t>39580; 70053</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>65570; 102786</t>
+          <t>66232; 102817</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38607; 68429</t>
+          <t>37856; 69409</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>52198; 156152</t>
+          <t>102691; 149453</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>42852; 74136</t>
+          <t>42035; 73397</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>85666; 124037</t>
+          <t>85072; 126247</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59533; 95627</t>
+          <t>58883; 94903</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>112291; 145544</t>
+          <t>125575; 162048</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>88444; 128260</t>
+          <t>87166; 130516</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>159271; 211393</t>
+          <t>159570; 215212</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>104847; 152251</t>
+          <t>105835; 151758</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>161070; 286541</t>
+          <t>240686; 299142</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88974</t>
+          <t>96243</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>286809</t>
+          <t>99751</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>375783</t>
+          <t>195994</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>28456; 54369</t>
+          <t>28463; 53415</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>42630; 73640</t>
+          <t>42693; 74713</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15402; 35979</t>
+          <t>15818; 35302</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>70780; 108565</t>
+          <t>77590; 117136</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>29904; 54650</t>
+          <t>28935; 54743</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>47694; 83723</t>
+          <t>50578; 83180</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28496; 54700</t>
+          <t>28509; 55133</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>98240; 603392</t>
+          <t>83533; 116436</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>63162; 97419</t>
+          <t>63061; 98851</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>99884; 144960</t>
+          <t>99713; 142376</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>49783; 85084</t>
+          <t>49004; 83069</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>186535; 776728</t>
+          <t>172983; 221345</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>75733</t>
+          <t>77657</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>92787</t>
+          <t>103580</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>168520</t>
+          <t>181237</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>38974; 67107</t>
+          <t>38846; 67587</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53694; 91432</t>
+          <t>56345; 91499</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>51412; 81439</t>
+          <t>51416; 82503</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>61379; 92070</t>
+          <t>63745; 94666</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>63138; 98671</t>
+          <t>65680; 100155</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>82809; 122937</t>
+          <t>81959; 121255</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>64970; 102571</t>
+          <t>65513; 102030</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>73245; 111675</t>
+          <t>88048; 121331</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>112754; 156576</t>
+          <t>110670; 154801</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>149444; 201345</t>
+          <t>146042; 200232</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>124625; 176006</t>
+          <t>126243; 173320</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>141251; 193633</t>
+          <t>161040; 206920</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>361991</t>
+          <t>383676</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>584109</t>
+          <t>427416</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>946100</t>
+          <t>811091</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>140911; 188514</t>
+          <t>138475; 189999</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>222019; 282813</t>
+          <t>218116; 285421</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>162097; 216780</t>
+          <t>163918; 217219</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>280643; 412039</t>
+          <t>346484; 422103</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>185394; 242778</t>
+          <t>182438; 241226</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>289062; 360613</t>
+          <t>287533; 360504</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>215180; 277386</t>
+          <t>213063; 274503</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>390238; 1157341</t>
+          <t>398113; 463994</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>341330; 414212</t>
+          <t>338008; 411953</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>527858; 621491</t>
+          <t>527790; 627280</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>389233; 476535</t>
+          <t>392156; 470234</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>736831; 1507037</t>
+          <t>764914; 862677</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_fisi_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2A_fisi_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad física (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad física (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad física (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad física (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
